--- a/results/count/542_WT__2_z06c1-2/measurements.xlsx
+++ b/results/count/542_WT__2_z06c1-2/measurements.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,189 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>v2-raw / pre-validation -- stats below over interior (on_border=False) lacunae only</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2004.4118</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1720</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1474.8632</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>major_axis_length</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>88.87260000000001</v>
+      </c>
+      <c r="C7" t="n">
+        <v>77.8309</v>
+      </c>
+      <c r="D7" t="n">
+        <v>44.7578</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>minor_axis_length</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>29.1534</v>
+      </c>
+      <c r="C8" t="n">
+        <v>29.6128</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10.3063</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>aspect_ratio</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.1061</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.0469</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.2971</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>eccentricity</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.9105</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9446</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.0696</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>solidity</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.7736</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.7956</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1245</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>17</v>
       </c>
     </row>

--- a/results/count/542_WT__2_z06c1-2/measurements.xlsx
+++ b/results/count/542_WT__2_z06c1-2/measurements.xlsx
@@ -446,13 +446,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -501,13 +501,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2004.4118</v>
+        <v>2541.7692</v>
       </c>
       <c r="C6" t="n">
-        <v>1720</v>
+        <v>3013</v>
       </c>
       <c r="D6" t="n">
-        <v>1474.8632</v>
+        <v>1427.4432</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>88.87260000000001</v>
+        <v>108.2371</v>
       </c>
       <c r="C7" t="n">
-        <v>77.8309</v>
+        <v>124.4642</v>
       </c>
       <c r="D7" t="n">
-        <v>44.7578</v>
+        <v>40.2415</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29.1534</v>
+        <v>31.7238</v>
       </c>
       <c r="C8" t="n">
-        <v>29.6128</v>
+        <v>33.1799</v>
       </c>
       <c r="D8" t="n">
-        <v>10.3063</v>
+        <v>10.2747</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -573,13 +573,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.1061</v>
+        <v>3.5771</v>
       </c>
       <c r="C9" t="n">
-        <v>3.0469</v>
+        <v>3.6285</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2971</v>
+        <v>1.3089</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
@@ -597,13 +597,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9105</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9446</v>
+        <v>0.9613</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0696</v>
+        <v>0.0596</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7736</v>
+        <v>0.7472</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7956</v>
+        <v>0.7672</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1245</v>
+        <v>0.1322</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -649,7 +649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -959,31 +959,31 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>429</v>
+        <v>2177</v>
       </c>
       <c r="C8" t="n">
-        <v>32.6683</v>
+        <v>80.2406</v>
       </c>
       <c r="D8" t="n">
-        <v>18.0955</v>
+        <v>35.2894</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8053</v>
+        <v>2.2738</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8326</v>
+        <v>0.8981</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9186</v>
+        <v>0.8959</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1358</v>
+        <v>-0.0663</v>
       </c>
       <c r="I8" t="n">
-        <v>310.6946</v>
+        <v>304.0032</v>
       </c>
       <c r="J8" t="n">
-        <v>230.2191</v>
+        <v>624.6292999999999</v>
       </c>
       <c r="K8" t="b">
         <v>0</v>
@@ -999,31 +999,31 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>603</v>
+        <v>3251</v>
       </c>
       <c r="C9" t="n">
-        <v>61.214</v>
+        <v>124.4642</v>
       </c>
       <c r="D9" t="n">
-        <v>16.9081</v>
+        <v>40.9538</v>
       </c>
       <c r="E9" t="n">
-        <v>3.6204</v>
+        <v>3.0391</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9611</v>
+        <v>0.9443</v>
       </c>
       <c r="G9" t="n">
-        <v>0.702</v>
+        <v>0.639</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5376</v>
+        <v>0.028</v>
       </c>
       <c r="I9" t="n">
-        <v>350.4892</v>
+        <v>423.426</v>
       </c>
       <c r="J9" t="n">
-        <v>219.5837</v>
+        <v>66.5638</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -1039,31 +1039,31 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>2177</v>
+        <v>3239</v>
       </c>
       <c r="C10" t="n">
-        <v>80.2406</v>
+        <v>125.7671</v>
       </c>
       <c r="D10" t="n">
-        <v>35.2894</v>
+        <v>33.4856</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2738</v>
+        <v>3.7559</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8981</v>
+        <v>0.9639</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8959</v>
+        <v>0.9114</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0663</v>
+        <v>-0.0886</v>
       </c>
       <c r="I10" t="n">
-        <v>304.0032</v>
+        <v>481.7314</v>
       </c>
       <c r="J10" t="n">
-        <v>624.6292999999999</v>
+        <v>573.2766</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
@@ -1079,31 +1079,31 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>1720</v>
+        <v>3188</v>
       </c>
       <c r="C11" t="n">
-        <v>77.8309</v>
+        <v>122.408</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7243</v>
+        <v>33.7355</v>
       </c>
       <c r="E11" t="n">
-        <v>2.1787</v>
+        <v>3.6285</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8884</v>
+        <v>0.9613</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6703</v>
+        <v>0.8804</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3576</v>
+        <v>-0.0452</v>
       </c>
       <c r="I11" t="n">
-        <v>398.6076</v>
+        <v>529.6236</v>
       </c>
       <c r="J11" t="n">
-        <v>66.8616</v>
+        <v>391.0301</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
@@ -1119,31 +1119,31 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>1531</v>
+        <v>3013</v>
       </c>
       <c r="C12" t="n">
-        <v>58.6194</v>
+        <v>170.6455</v>
       </c>
       <c r="D12" t="n">
-        <v>35.5952</v>
+        <v>29.6128</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6468</v>
+        <v>5.7626</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7945</v>
+        <v>0.9848</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8417</v>
+        <v>0.5248</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3258</v>
+        <v>-0.2083</v>
       </c>
       <c r="I12" t="n">
-        <v>451.3083</v>
+        <v>594.9578</v>
       </c>
       <c r="J12" t="n">
-        <v>66.22929999999999</v>
+        <v>912.8117999999999</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
@@ -1159,31 +1159,31 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>3239</v>
+        <v>3414</v>
       </c>
       <c r="C13" t="n">
-        <v>125.7671</v>
+        <v>148.9986</v>
       </c>
       <c r="D13" t="n">
-        <v>33.4856</v>
+        <v>33.1799</v>
       </c>
       <c r="E13" t="n">
-        <v>3.7559</v>
+        <v>4.4906</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9639</v>
+        <v>0.9749</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9114</v>
+        <v>0.8294</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0886</v>
+        <v>-0.0805</v>
       </c>
       <c r="I13" t="n">
-        <v>481.7314</v>
+        <v>580.5811</v>
       </c>
       <c r="J13" t="n">
-        <v>573.2766</v>
+        <v>782.628</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
@@ -1199,31 +1199,31 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>3188</v>
+        <v>4647</v>
       </c>
       <c r="C14" t="n">
-        <v>122.408</v>
+        <v>139.2144</v>
       </c>
       <c r="D14" t="n">
-        <v>33.7355</v>
+        <v>45.6902</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6285</v>
+        <v>3.0469</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9613</v>
+        <v>0.9446</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8804</v>
+        <v>0.8623</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0452</v>
+        <v>-0.0076</v>
       </c>
       <c r="I14" t="n">
-        <v>529.6236</v>
+        <v>723.0331</v>
       </c>
       <c r="J14" t="n">
-        <v>391.0301</v>
+        <v>247.2671</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
@@ -1239,31 +1239,31 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>3013</v>
+        <v>1123</v>
       </c>
       <c r="C15" t="n">
-        <v>170.6455</v>
+        <v>92.9757</v>
       </c>
       <c r="D15" t="n">
-        <v>29.6128</v>
+        <v>18.8182</v>
       </c>
       <c r="E15" t="n">
-        <v>5.7626</v>
+        <v>4.9407</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9848</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5248</v>
+        <v>0.6997</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2083</v>
+        <v>-0.1287</v>
       </c>
       <c r="I15" t="n">
-        <v>594.9578</v>
+        <v>817.2876</v>
       </c>
       <c r="J15" t="n">
-        <v>912.8117999999999</v>
+        <v>724.4328</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
@@ -1279,34 +1279,34 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>3414</v>
+        <v>3750</v>
       </c>
       <c r="C16" t="n">
-        <v>148.9986</v>
+        <v>145.2582</v>
       </c>
       <c r="D16" t="n">
-        <v>33.1799</v>
+        <v>33.093</v>
       </c>
       <c r="E16" t="n">
-        <v>4.4906</v>
+        <v>4.3894</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9749</v>
+        <v>0.9737</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8294</v>
+        <v>0.8965</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0805</v>
+        <v>-0.0485</v>
       </c>
       <c r="I16" t="n">
-        <v>580.5811</v>
+        <v>952.2043</v>
       </c>
       <c r="J16" t="n">
-        <v>782.628</v>
+        <v>400.2763</v>
       </c>
       <c r="K16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1319,196 +1319,36 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>4647</v>
+        <v>1341</v>
       </c>
       <c r="C17" t="n">
-        <v>139.2144</v>
+        <v>90.1135</v>
       </c>
       <c r="D17" t="n">
-        <v>45.6902</v>
+        <v>19.5596</v>
       </c>
       <c r="E17" t="n">
-        <v>3.0469</v>
+        <v>4.6071</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9446</v>
+        <v>0.9762</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8623</v>
+        <v>0.911</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0076</v>
+        <v>-0.0956</v>
       </c>
       <c r="I17" t="n">
-        <v>723.0331</v>
+        <v>984.7517</v>
       </c>
       <c r="J17" t="n">
-        <v>247.2671</v>
+        <v>948.2617</v>
       </c>
       <c r="K17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="n">
-        <v>647</v>
-      </c>
-      <c r="C18" t="n">
-        <v>57.53</v>
-      </c>
-      <c r="D18" t="n">
-        <v>17.4897</v>
-      </c>
-      <c r="E18" t="n">
-        <v>3.2894</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.9527</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.763</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-0.0276</v>
-      </c>
-      <c r="I18" t="n">
-        <v>800.4884</v>
-      </c>
-      <c r="J18" t="n">
-        <v>727.0726</v>
-      </c>
-      <c r="K18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="n">
-        <v>476</v>
-      </c>
-      <c r="C19" t="n">
-        <v>33.3296</v>
-      </c>
-      <c r="D19" t="n">
-        <v>19.1581</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1.7397</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.8183</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.8799</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-0.1394</v>
-      </c>
-      <c r="I19" t="n">
-        <v>840.1218</v>
-      </c>
-      <c r="J19" t="n">
-        <v>720.8445</v>
-      </c>
-      <c r="K19" t="b">
-        <v>0</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="n">
-        <v>3750</v>
-      </c>
-      <c r="C20" t="n">
-        <v>145.2582</v>
-      </c>
-      <c r="D20" t="n">
-        <v>33.093</v>
-      </c>
-      <c r="E20" t="n">
-        <v>4.3894</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.9737</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.8965</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-0.0485</v>
-      </c>
-      <c r="I20" t="n">
-        <v>952.2043</v>
-      </c>
-      <c r="J20" t="n">
-        <v>400.2763</v>
-      </c>
-      <c r="K20" t="b">
-        <v>1</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="n">
-        <v>1341</v>
-      </c>
-      <c r="C21" t="n">
-        <v>90.1135</v>
-      </c>
-      <c r="D21" t="n">
-        <v>19.5596</v>
-      </c>
-      <c r="E21" t="n">
-        <v>4.6071</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.9762</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.911</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-0.0956</v>
-      </c>
-      <c r="I21" t="n">
-        <v>984.7517</v>
-      </c>
-      <c r="J21" t="n">
-        <v>948.2617</v>
-      </c>
-      <c r="K21" t="b">
-        <v>1</v>
-      </c>
-      <c r="L21" t="inlineStr">
         <is>
           <t>px</t>
         </is>
